--- a/bancos/manual/memoria_calculo.xlsx
+++ b/bancos/manual/memoria_calculo.xlsx
@@ -2273,8 +2273,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -2553,20 +2553,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3A4A5B7-B008-4619-B816-1F4ADC3379B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
-    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF63902A-4FCC-4911-9FD6-D921F35389BE}"/>
 </file>